--- a/questionnaire_templates/022_energy_flow_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/022_energy_flow_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'site_name',_'label':_'site_name',_'type':_'text'}</t>
+          <t>site_name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'site_name', 'label': 'Site Name', 'type': 'text'}</t>
+          <t>Site Name</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'site_id',_'label':_'site_id',_'type':_'text'}</t>
+          <t>site_id</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'site_id', 'label': 'Site ID', 'type': 'text'}</t>
+          <t>Site ID</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'site_location',_'label':_'site_location',_'type':_'text'}</t>
+          <t>site_location</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'site_location', 'label': 'Site Location', 'type': 'text'}</t>
+          <t>Site Location</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'site_capacity',_'label':_'site_capacity',_'type':_'integer'}</t>
+          <t>site_capacity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'site_capacity', 'label': 'Site Capacity', 'type': 'integer'}</t>
+          <t>Site Capacity</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'site_inflow',_'label':_'site_inflow',_'type':_'text'}</t>
+          <t>site_inflow</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'site_inflow', 'label': 'Site Inflow', 'type': 'text'}</t>
+          <t>Site Inflow</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'process_inflow',_'label':_'process_inflow',_'type':_'text'}</t>
+          <t>process_inflow</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'process_inflow', 'label': 'Process Inflow', 'type': 'text'}</t>
+          <t>Process Inflow</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'transmission_inflow',_'label':_'transmission_inflow',_'type':_'text'}</t>
+          <t>transmission_inflow</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'transmission_inflow', 'label': 'Transmission Inflow', 'type': 'text'}</t>
+          <t>Transmission Inflow</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'distribution_inflow',_'label':_'distribution_inflow',_'type':_'text'}</t>
+          <t>distribution_inflow</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'distribution_inflow', 'label': 'Distribution Inflow', 'type': 'text'}</t>
+          <t>Distribution Inflow</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'site_outflow',_'label':_'site_outflow',_'type':_'text'}</t>
+          <t>site_outflow</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'site_outflow', 'label': 'Site Outflow', 'type': 'text'}</t>
+          <t>Site Outflow</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'process_outflow',_'label':_'process_outflow',_'type':_'text'}</t>
+          <t>process_outflow</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'process_outflow', 'label': 'Process Outflow', 'type': 'text'}</t>
+          <t>Process Outflow</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'transmission_outflow',_'label':_'transmission_outflow',_'type':_'text'}</t>
+          <t>transmission_outflow</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'transmission_outflow', 'label': 'Transmission Outflow', 'type': 'text'}</t>
+          <t>Transmission Outflow</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'distribution_outflow',_'label':_'distribution_outflow',_'type':_'text'}</t>
+          <t>distribution_outflow</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'distribution_outflow', 'label': 'Distribution Outflow', 'type': 'text'}</t>
+          <t>Distribution Outflow</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'site_equip_loss',_'label':_'site_equipment_loss',_'type':_'text'}</t>
+          <t>site_equipment_loss</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'site_equip_loss', 'label': 'Site Equipment Loss', 'type': 'text'}</t>
+          <t>Site Equipment Loss</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pipe_leakage',_'label':_'pipe_leakage',_'type':_'text'}</t>
+          <t>pipe_leakage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'pipe_leakage', 'label': 'Pipe Leakage', 'type': 'text'}</t>
+          <t>Pipe Leakage</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'heat_gain_loss',_'label':_'heat_gain_loss',_'type':_'text'}</t>
+          <t>heat_gain_loss</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'heat_gain_loss', 'label': 'Heat Gain Loss', 'type': 'text'}</t>
+          <t>Heat Gain Loss</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'transmission_loss',_'label':_'transmission_loss',_'type':_'text'}</t>
+          <t>transmission_loss</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'transmission_loss', 'label': 'Transmission Loss', 'type': 'text'}</t>
+          <t>Transmission Loss</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'distribution_loss',_'label':_'distribution_loss',_'type':_'text'}</t>
+          <t>distribution_loss</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'distribution_loss', 'label': 'Distribution Loss', 'type': 'text'}</t>
+          <t>Distribution Loss</t>
         </is>
       </c>
     </row>
